--- a/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
+++ b/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\game-dev-team\docs\contrary-survivor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB6AD851-B722-4982-9794-5029C3204DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6F1DF63-4E5D-4563-9168-1653778D6470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -97,37 +97,6 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Этап D — Оружие (визуал + механика) + сочность боя</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-D1–D3 Держание пистолета, вспышка выстрела, след пули; удар ножа — передний взмах/сектор: 1–2 цели впереди, НЕ круговой урон вокруг игрока (ADR-037).
-D4 Модели оружия приняты (пистолет 240 трис, нож 80).
-D5 Сочность боя: всплывающие цифры урона + микро-заморозка удара + тряска экрана.
-D6 Пакетом: бандиты получают огнестрел + боевая камера (ADR-035) — в бою камера смещается к угрозе (без отдаления), враг не стреляет, если он вне кадра.
-D7 Ограничения ИИ (ADR-036): безопасная деревня (враги не заходят) + «поводок» — гонятся только в радиусе своей базы.
-Плотность боя: одновременно активны не больше 2–3 врагов (ADR-037).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>Этап E — Прогрессия: броня</t>
     </r>
     <r>
@@ -451,6 +420,29 @@
 0.2 Оружие: пистолет + нож.
 0.3 Сейв / смерть / респаун.
 0.4 Магазин торговца.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Этап D — Оружие (визуал + механика) + сочность боя</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+D1–D3 Держание пистолета, вспышка выстрела, след пули; удар ножа — передний взмах/сектор: 1–2 цели впереди, НЕ круговой урон вокруг игрока (ADR-037).
+D4 Модели оружия приняты (пистолет 240 трис, нож 80).
+D5 Сочность боя: всплывающие цифры урона + микро-заморозка удара + тряска экрана.
+D6 Пакетом: бандиты получают огнестрел + боевая камера (ADR-035) — в бою камера смещается к угрозе (без отдаления), враг не стреляет, если он вне кадра.
+D7 Ограничения ИИ (ADR-036): безопасная деревня (враги не заходят) + «поводок» — гонятся только в радиусе своей базы.
+D8 Темповый фикс (ADR-040): по одной точке интереса на пути к каждой базе (реюз пропсов). Скорость не трогаем — игрок и так быстрый. Полные POI с лутом — этап M.
+Плотность боя: одновременно активны не больше 2–3 врагов (ADR-037).</t>
     </r>
   </si>
 </sst>
@@ -607,7 +599,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -642,15 +634,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -879,12 +874,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="16"/>
     </row>
     <row r="2" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -908,7 +903,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>6</v>
@@ -922,7 +917,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>7</v>
@@ -936,7 +931,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>8</v>
@@ -950,19 +945,19 @@
         <v>5</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="128.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="138" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>5</v>
       </c>
       <c r="B7" s="10"/>
-      <c r="C7" s="15" t="s">
-        <v>20</v>
+      <c r="C7" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>10</v>
@@ -973,8 +968,8 @@
         <v>6</v>
       </c>
       <c r="B8" s="10"/>
-      <c r="C8" s="15" t="s">
-        <v>21</v>
+      <c r="C8" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>11</v>
@@ -985,8 +980,8 @@
         <v>7</v>
       </c>
       <c r="B9" s="10"/>
-      <c r="C9" s="15" t="s">
-        <v>22</v>
+      <c r="C9" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>12</v>
@@ -997,8 +992,8 @@
         <v>8</v>
       </c>
       <c r="B10" s="10"/>
-      <c r="C10" s="15" t="s">
-        <v>23</v>
+      <c r="C10" s="12" t="s">
+        <v>22</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>13</v>
@@ -1009,8 +1004,8 @@
         <v>9</v>
       </c>
       <c r="B11" s="10"/>
-      <c r="C11" s="15" t="s">
-        <v>24</v>
+      <c r="C11" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>14</v>
@@ -1021,8 +1016,8 @@
         <v>10</v>
       </c>
       <c r="B12" s="10"/>
-      <c r="C12" s="15" t="s">
-        <v>25</v>
+      <c r="C12" s="12" t="s">
+        <v>24</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>15</v>
@@ -1033,8 +1028,8 @@
         <v>11</v>
       </c>
       <c r="B13" s="10"/>
-      <c r="C13" s="15" t="s">
-        <v>26</v>
+      <c r="C13" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>16</v>
@@ -1045,8 +1040,8 @@
         <v>12</v>
       </c>
       <c r="B14" s="10"/>
-      <c r="C14" s="15" t="s">
-        <v>27</v>
+      <c r="C14" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>17</v>
@@ -1057,8 +1052,8 @@
         <v>13</v>
       </c>
       <c r="B15" s="10"/>
-      <c r="C15" s="15" t="s">
-        <v>28</v>
+      <c r="C15" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>18</v>
@@ -1069,15 +1064,15 @@
         <v>14</v>
       </c>
       <c r="B16" s="10"/>
-      <c r="C16" s="15" t="s">
-        <v>29</v>
+      <c r="C16" s="12" t="s">
+        <v>28</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="16"/>
+      <c r="C17" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
+++ b/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\game-dev-team\docs\contrary-survivor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6F1DF63-4E5D-4563-9168-1653778D6470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6012069D-3096-4665-8DF2-BD2CB2DA1EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>ContrarySurvivor — план демки (тестируемый и монетизируемый срез)</t>
   </si>
@@ -444,6 +444,9 @@
 D8 Темповый фикс (ADR-040): по одной точке интереса на пути к каждой базе (реюз пропсов). Скорость не трогаем — игрок и так быстрый. Полные POI с лутом — этап M.
 Плотность боя: одновременно активны не больше 2–3 врагов (ADR-037).</t>
     </r>
+  </si>
+  <si>
+    <t>🔄</t>
   </si>
 </sst>
 </file>
@@ -638,14 +641,14 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -874,12 +877,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="16"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="17"/>
     </row>
     <row r="2" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -955,8 +958,10 @@
       <c r="A7" s="9">
         <v>5</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="17" t="s">
+      <c r="B7" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>33</v>
       </c>
       <c r="D7" s="11" t="s">

--- a/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
+++ b/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\game-dev-team\docs\contrary-survivor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6012069D-3096-4665-8DF2-BD2CB2DA1EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0934756F-FEBB-4A64-B708-066F673443A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -423,30 +423,19 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>Этап D — Оружие (визуал + механика) + сочность боя</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t>🔄</t>
+  </si>
+  <si>
+    <t>Этап D — Оружие (визуал + механика) + сочность боя
 D1–D3 Держание пистолета, вспышка выстрела, след пули; удар ножа — передний взмах/сектор: 1–2 цели впереди, НЕ круговой урон вокруг игрока (ADR-037).
 D4 Модели оружия приняты (пистолет 240 трис, нож 80).
 D5 Сочность боя: всплывающие цифры урона + микро-заморозка удара + тряска экрана.
 D6 Пакетом: бандиты получают огнестрел + боевая камера (ADR-035) — в бою камера смещается к угрозе (без отдаления), враг не стреляет, если он вне кадра.
 D7 Ограничения ИИ (ADR-036): безопасная деревня (враги не заходят) + «поводок» — гонятся только в радиусе своей базы.
 D8 Темповый фикс (ADR-040): по одной точке интереса на пути к каждой базе (реюз пропсов). Скорость не трогаем — игрок и так быстрый. Полные POI с лутом — этап M.
-Плотность боя: одновременно активны не больше 2–3 врагов (ADR-037).</t>
-    </r>
-  </si>
-  <si>
-    <t>🔄</t>
+Плотность боя: одновременно активны не больше 2–3 врагов (ADR-037).
+D9. Журнал заданий в экране инвентаря (инвентарь слева, задания справа; без отдельной кнопки) + фикс маркера: после выполнения условий вести к квестодателю (вопрос издателю отправлен)
+D10. Обыск контейнеров: подсветка машины/ящика при подходе, кнопка действия, окно «инвентарь слева / находки справа» как в LDoE (вопрос издателю: Build 1 или Build 2)</t>
   </si>
 </sst>
 </file>
@@ -954,15 +943,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="138" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="195" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>5</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>34</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>33</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>10</v>

--- a/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
+++ b/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\game-dev-team\docs\contrary-survivor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0934756F-FEBB-4A64-B708-066F673443A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{597F7C6E-875C-4EE0-B7F8-705DE92033A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2200" yWindow="2200" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
   <si>
     <t>ContrarySurvivor — план демки (тестируемый и монетизируемый срез)</t>
   </si>
@@ -423,9 +423,6 @@
     </r>
   </si>
   <si>
-    <t>🔄</t>
-  </si>
-  <si>
     <t>Этап D — Оружие (визуал + механика) + сочность боя
 D1–D3 Держание пистолета, вспышка выстрела, след пули; удар ножа — передний взмах/сектор: 1–2 цели впереди, НЕ круговой урон вокруг игрока (ADR-037).
 D4 Модели оружия приняты (пистолет 240 трис, нож 80).
@@ -435,7 +432,14 @@
 D8 Темповый фикс (ADR-040): по одной точке интереса на пути к каждой базе (реюз пропсов). Скорость не трогаем — игрок и так быстрый. Полные POI с лутом — этап M.
 Плотность боя: одновременно активны не больше 2–3 врагов (ADR-037).
 D9. Журнал заданий в экране инвентаря (инвентарь слева, задания справа; без отдельной кнопки) + фикс маркера: после выполнения условий вести к квестодателю (вопрос издателю отправлен)
-D10. Обыск контейнеров: подсветка машины/ящика при подходе, кнопка действия, окно «инвентарь слева / находки справа» как в LDoE (вопрос издателю: Build 1 или Build 2)</t>
+D10. Обыск контейнеров: подсветка машины/ящика при подходе, кнопка действия, окно «инвентарь слева / находки справа» как в LDoE (вопрос издателю: Build 1 или Build 2)
+Дополнительно (сверх плана этапа):
+- Экипировка Т0-Т3: 12 модульных мешей (одежда + 3 тира брони) заведены в игру
+- Броня Т1-Т3 продаётся у торговца (по 5 монет) + прокрутка списка товаров колесом мыши
+- Модель старосты по референсу: 3 модульных меша, надета на NPC в деревне
+- Фикс: старая броня при замене возвращается в рюкзак (не пропадает)
+- Фикс: починен сломанный материал экипировки (была серая заглушка)
+- Промпты для нейронки: внешность старосты и торговца (по 2 комплекта)</t>
   </si>
 </sst>
 </file>
@@ -943,15 +947,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="195" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="286" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>5</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>33</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>34</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>10</v>

--- a/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
+++ b/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\game-dev-team\docs\contrary-survivor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{597F7C6E-875C-4EE0-B7F8-705DE92033A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E827EBF-D745-486E-9247-29D0872BE416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2200" yWindow="2200" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
   <si>
     <t>ContrarySurvivor — план демки (тестируемый и монетизируемый срез)</t>
   </si>
@@ -85,33 +85,6 @@
   </si>
   <si>
     <t>Минимальный темповый фикс (ориентир/скорость/спринт) — в Этапе D; здесь расширенный слой после валидации.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Этап E — Прогрессия: броня</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-E1 Броня влияет на получаемый урон — модификатор защиты в UStatsComponent (ADR-015).
-E2 Один комплект брони как апгрейд в магазине торговца (переиспользуем существующие модульные меши, новый арт не делаем).</t>
-    </r>
   </si>
   <si>
     <r>
@@ -440,6 +413,18 @@
 - Фикс: старая броня при замене возвращается в рюкзак (не пропадает)
 - Фикс: починен сломанный материал экипировки (была серая заглушка)
 - Промпты для нейронки: внешность старосты и торговца (по 2 комплекта)</t>
+  </si>
+  <si>
+    <t>Этап E — Прогрессия: броня
+E1 Броня влияет на получаемый урон — модификатор защиты в UStatsComponent (ADR-015).
+E2 Один комплект брони как апгрейд в магазине торговца (переиспользуем существующие модульные меши, новый арт не делаем).
+Дополнительно (сверх плана этапа):
+- Игрок начинает совсем без брони; стартовый облик — одежда Т0 (не предмет, защиты не даёт), белого манекена больше нет
+- 9 новых иконок предметов брони (нарисованы concept, утверждены Ринатом) + иконки пустых слотов заведены в игру
+- Инвентарь: иконки в слотах, строка «Защита: N%», подписи переведены на русский
+- Магазин: показ прибавки защиты у брони до покупки; старая броня _01 убрана из каталога (ассет цел)
+- Цены (50/120/250 за слот) и защита тиров — настраиваемые на размещённом экземпляре в редакторе
+- Новый автотест «после старта защита нулевая»; сборка и тесты — независимый прогон qa</t>
   </si>
 </sst>
 </file>
@@ -899,7 +884,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>6</v>
@@ -913,7 +898,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>7</v>
@@ -927,7 +912,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>8</v>
@@ -941,7 +926,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>9</v>
@@ -955,19 +940,21 @@
         <v>5</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="45.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="125" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>6</v>
       </c>
-      <c r="B8" s="10"/>
+      <c r="B8" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="C8" s="12" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>11</v>
@@ -979,7 +966,7 @@
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>12</v>
@@ -991,7 +978,7 @@
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>13</v>
@@ -1003,7 +990,7 @@
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>14</v>
@@ -1015,7 +1002,7 @@
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>15</v>
@@ -1027,7 +1014,7 @@
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>16</v>
@@ -1039,7 +1026,7 @@
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>17</v>
@@ -1051,7 +1038,7 @@
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>18</v>
@@ -1063,7 +1050,7 @@
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>19</v>

--- a/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
+++ b/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\game-dev-team\docs\contrary-survivor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E827EBF-D745-486E-9247-29D0872BE416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565918FB-7837-4E12-A313-07DD1E9E44A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
   <si>
     <t>ContrarySurvivor — план демки (тестируемый и монетизируемый срез)</t>
   </si>
@@ -85,35 +85,6 @@
   </si>
   <si>
     <t>Минимальный темповый фикс (ориентир/скорость/спринт) — в Этапе D; здесь расширенный слой после валидации.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Этап F — Удержание: онбординг + ежедневка + аналитика</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-F1 Онбординг первых 5 минут: контекстные подсказки управления + ранняя победа (волки → 150 монет) + подача крючка «ноутбук — кто охотится за героем».
-F1+ Метка цели квеста после взятия (направляющая стрелка, как у старосты/торговца — реюз маркеров NPC).
-F2 Ежедневная награда за вход (попап + учёт даты + выдача).
-F3 Аналитика GameAnalytics (ADR-038): события старта сессии / убийств / квестов / покупок / смертей + метрики удержания D1/D3/D7.</t>
-    </r>
   </si>
   <si>
     <r>
@@ -197,33 +168,6 @@
 HUD, магазин, диалоги, экран смерти, инвентарь с иконками → UMG (логика в C++-базе, внешний вид в BP-виджетах WBP_*).
 Новые экраны (онбординг, ежедневка, цифры урона) сразу делаются лёгкими UMG-виджетами.
 Миникарта — в будущем, после тест-билда (до неё игрока ведут метки целей).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Этап J — Таблицы данных: квесты и предметы</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-DT_Quests / DT_Items — контент задаётся таблицами (масштабирование без правки кода).
-Заодно закрыть тех-долг сохранений (имена и стопки предметов).</t>
     </r>
   </si>
   <si>
@@ -425,6 +369,51 @@
 - Магазин: показ прибавки защиты у брони до покупки; старая броня _01 убрана из каталога (ассет цел)
 - Цены (50/120/250 за слот) и защита тиров — настраиваемые на размещённом экземпляре в редакторе
 - Новый автотест «после старта защита нулевая»; сборка и тесты — независимый прогон qa</t>
+  </si>
+  <si>
+    <r>
+      <t>Этап J — Таблицы данных: квесты и предметы</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+DT_Quests / DT_Items — контент задаётся таблицами (масштабирование без правки кода).
+Заодно закрыть тех-долг сохранений (имена и стопки предметов).
+Единый лут-конфиг по образцу STALKER (ADR-045): вся настройка выпадения добычи с врагов — в одной таблице данных (что падает, с каким шансом и в каком количестве); у врага есть ранг-опытность, который улучшает добычу (опытный враг даёт лут лучше, новичок — хуже); правится в редакторе без программиста.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Этап F — Удержание: онбординг + ежедневка + аналитика</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+F1 Онбординг первых 5 минут: контекстные подсказки управления + ранняя победа (волки → 150 монет) + подача крючка «ноутбук — кто охотится за героем».
+F1+ Метка цели квеста после взятия (направляющая стрелка, как у старосты/торговца — реюз маркеров NPC).
+F2 Ежедневная награда за вход (попап + учёт даты + выдача).
+F3 Аналитика GameAnalytics (ADR-038): события старта сессии / убийств / квестов / покупок / смертей + метрики удержания D1/D3/D7.
+Дополнительно (сверх плана этапа):
+Лут бандитов: деньги + 1-2 расходника с равной вероятностью из настраиваемой таблицы (Консервы / Вода / Бинт), русские имена расходников во всей игре (решения Рината 07-17).
+Звук: исправлены бесконечные «охи» при попадании (короткий случайный кусок звука + защита от спама), выстрел вдвое громче; птички и шаги не тронуты.
+Для аналитики заведён латинский идентификатор товара — русские имена ломали бы статистику покупок.
+Починена тестовая обвязка: тест NavWalkingFixed позеленел (15 из 16 зелёных).
+Правки по приёмке 07-12: тон диалога Q3 (староста предлагает, а не приказывает), высота панели диалога по числу строк, метки квестов работают в BP из коробки.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -503,7 +492,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -525,6 +514,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,7 +575,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -619,6 +614,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -633,6 +643,12 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF66FF66"/>
+      <color rgb="FF99FF99"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -855,12 +871,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="17"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="22"/>
     </row>
     <row r="2" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -884,7 +900,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>6</v>
@@ -898,7 +914,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>7</v>
@@ -912,7 +928,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>8</v>
@@ -926,47 +942,49 @@
         <v>5</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="286" x14ac:dyDescent="0.25">
-      <c r="A7" s="9">
+      <c r="A7" s="14">
         <v>5</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="11" t="s">
+      <c r="C7" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="17" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="125" x14ac:dyDescent="0.25">
-      <c r="A8" s="9">
+      <c r="A8" s="14">
         <v>6</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="11" t="s">
+      <c r="C8" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="75.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="188" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>7</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="12" t="s">
-        <v>20</v>
+      <c r="B9" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>33</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>12</v>
@@ -978,7 +996,7 @@
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>13</v>
@@ -990,7 +1008,7 @@
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>14</v>
@@ -1002,19 +1020,19 @@
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="38" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="75.5" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>11</v>
       </c>
       <c r="B13" s="10"/>
-      <c r="C13" s="12" t="s">
-        <v>24</v>
+      <c r="C13" s="19" t="s">
+        <v>32</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>16</v>
@@ -1026,7 +1044,7 @@
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>17</v>
@@ -1038,7 +1056,7 @@
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>18</v>
@@ -1050,7 +1068,7 @@
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>19</v>

--- a/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
+++ b/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\game-dev-team\docs\contrary-survivor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565918FB-7837-4E12-A313-07DD1E9E44A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{250F974A-DDF7-4AA1-BF57-0D328DBBEEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
   <si>
     <t>ContrarySurvivor — план демки (тестируемый и монетизируемый срез)</t>
   </si>
@@ -66,13 +66,7 @@
     <t>Build 1. Ориентиры удержания: D1 около 30% — хорошо, D7 — 8–10%.</t>
   </si>
   <si>
-    <t>Главный технический риск: Android ни разу не паковался. Build 1 мерит удержание D1/D7.</t>
-  </si>
-  <si>
     <t>Build 2 — после подтверждения удержания. Перед стартом — быстрая проверка выбранного рекламного плагина.</t>
-  </si>
-  <si>
-    <t>Объёмная работа; сдвигаема за Build 1, тест не блокирует.</t>
   </si>
   <si>
     <t>Для теста не обязателен, можно отложить.</t>
@@ -414,6 +408,17 @@
 Починена тестовая обвязка: тест NavWalkingFixed позеленел (15 из 16 зелёных).
 Правки по приёмке 07-12: тон диалога Q3 (староста предлагает, а не приказывает), высота панели диалога по числу строк, метки квестов работают в BP из коробки.</t>
     </r>
+  </si>
+  <si>
+    <t>🔄</t>
+  </si>
+  <si>
+    <t>Главный технический риск: Android ни разу не паковался. Build 1 мерит удержание D1/D7.
+07-17: конвейер собран, 2 APK проверены живью на realme (ADR-047), тач-управление принято Ринатом. Риск конвейера снят.</t>
+  </si>
+  <si>
+    <t>Объёмная работа; сдвигаема за Build 1, тест не блокирует.
+Стартован досрочно 07-18 по команде Рината (ADR-048): тач-слой и панели переводятся на UMG, ветка feature/umg-hud.</t>
   </si>
 </sst>
 </file>
@@ -900,7 +905,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>6</v>
@@ -914,7 +919,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>7</v>
@@ -928,7 +933,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>8</v>
@@ -942,7 +947,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>9</v>
@@ -956,7 +961,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>10</v>
@@ -970,7 +975,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>11</v>
@@ -984,22 +989,24 @@
         <v>5</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="75.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="75.5" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>8</v>
       </c>
-      <c r="B10" s="10"/>
+      <c r="B10" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="C10" s="12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="50.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1008,22 +1015,24 @@
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="52" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="50.5" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>10</v>
       </c>
-      <c r="B12" s="10"/>
+      <c r="B12" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="C12" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="75.5" x14ac:dyDescent="0.25">
@@ -1032,10 +1041,10 @@
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.25">
@@ -1044,10 +1053,10 @@
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="69" customHeight="1" x14ac:dyDescent="0.25">
@@ -1056,10 +1065,10 @@
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="56.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1068,10 +1077,10 @@
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
+++ b/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\game-dev-team\docs\contrary-survivor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{250F974A-DDF7-4AA1-BF57-0D328DBBEEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA16448-8C33-463B-842F-9D763AD5A69A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -418,7 +418,8 @@
   </si>
   <si>
     <t>Объёмная работа; сдвигаема за Build 1, тест не блокирует.
-Стартован досрочно 07-18 по команде Рината (ADR-048): тач-слой и панели переводятся на UMG, ветка feature/umg-hud.</t>
+Стартован досрочно 07-18 по команде Рината (ADR-048): тач-слой и панели переводятся на UMG, ветка feature/umg-hud.
+07-19: все 7 панелей переведены в UMG (генерация коммандлетом + назначение в слоты, verify вторым процессом, тесты 16/16). Получено ревью publisher: графика проходит, главная дыра - английские надписи и служебные имена в интерфейсе (ADR-049).</t>
   </si>
 </sst>
 </file>
@@ -1021,7 +1022,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="50.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="100" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>10</v>
       </c>

--- a/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
+++ b/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\game-dev-team\docs\contrary-survivor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA16448-8C33-463B-842F-9D763AD5A69A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C3FF4B-C36A-46A9-9971-4848DA579405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -79,35 +79,6 @@
   </si>
   <si>
     <t>Минимальный темповый фикс (ориентир/скорость/спринт) — в Этапе D; здесь расширенный слой после валидации.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Этап G — Android-сборка + замер → BUILD 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-G1 Первая Android-сборка (без Lumen/Nanite, запечённый свет, цвет в вершинах).
-G2 Замер: FPS на слабом устройстве, вес APK, минимальное устройство.
-G3 Раздача: закрытый тест RuStore (проверка) + небольшая VK Реклама на 200–300 «холодных» установок для честного замера D1/D7; сборку подписываем сами.
-Плюс дешёвый замер готовности смотреть рекламу заглушкой (без рекламной сети).</t>
-    </r>
   </si>
   <si>
     <r>
@@ -420,6 +391,32 @@
     <t>Объёмная работа; сдвигаема за Build 1, тест не блокирует.
 Стартован досрочно 07-18 по команде Рината (ADR-048): тач-слой и панели переводятся на UMG, ветка feature/umg-hud.
 07-19: все 7 панелей переведены в UMG (генерация коммандлетом + назначение в слоты, verify вторым процессом, тесты 16/16). Получено ревью publisher: графика проходит, главная дыра - английские надписи и служебные имена в интерфейсе (ADR-049).</t>
+  </si>
+  <si>
+    <r>
+      <t>Этап G — Android-сборка + замер → BUILD 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+G1 Первая Android-сборка (без Lumen/Nanite, запечённый свет, цвет в вершинах).
+G2 Замер: FPS на слабом устройстве, вес APK, минимальное устройство.
+G3 Раздача: закрытый тест RuStore (проверка) + небольшая VK Реклама на 200–300 «холодных» установок для честного замера D1/D7; сборку подписываем сами.
+Плюс дешёвый замер готовности смотреть рекламу заглушкой (без рекламной сети).
+Дополнительно (сверх плана этапа) — доводка Build 1 по живой приёмке (ADR-051):
+- Интро-сценка принята; кнопки диалога заменены на живые реплики героя.
+- Баннер ежедневной награды показывается после первого диалога со старостой, а не поверх интро.
+- Квест «Шкуры для торговца» упразднён: вместо него намёк старосты (торговец платит за шкуры, вторая стая к югу).
+- Новые инструменты для карты: спавнер волка возле игрока и граница мира (туман + невидимая стена); расстановка — Ринат.
+- Окна магазина и инвентаря пересобраны на канвас-раскладку для настройки мышкой (доводка выделения кнопок — в работе).</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -906,7 +903,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>6</v>
@@ -920,7 +917,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>7</v>
@@ -934,7 +931,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>8</v>
@@ -948,7 +945,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>9</v>
@@ -962,7 +959,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>10</v>
@@ -976,7 +973,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>11</v>
@@ -990,24 +987,24 @@
         <v>5</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="75.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="150.5" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>8</v>
       </c>
       <c r="B10" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>32</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="50.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1016,7 +1013,7 @@
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>13</v>
@@ -1027,13 +1024,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="75.5" x14ac:dyDescent="0.25">
@@ -1042,7 +1039,7 @@
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>14</v>
@@ -1054,7 +1051,7 @@
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>15</v>
@@ -1066,7 +1063,7 @@
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>16</v>
@@ -1078,7 +1075,7 @@
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>17</v>

--- a/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
+++ b/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\game-dev-team\docs\contrary-survivor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C3FF4B-C36A-46A9-9971-4848DA579405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD76C2DA-A487-404B-93CE-90DF5B782843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -393,19 +393,7 @@
 07-19: все 7 панелей переведены в UMG (генерация коммандлетом + назначение в слоты, verify вторым процессом, тесты 16/16). Получено ревью publisher: графика проходит, главная дыра - английские надписи и служебные имена в интерфейсе (ADR-049).</t>
   </si>
   <si>
-    <r>
-      <t>Этап G — Android-сборка + замер → BUILD 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t>Этап G — Android-сборка + замер → BUILD 1
 G1 Первая Android-сборка (без Lumen/Nanite, запечённый свет, цвет в вершинах).
 G2 Замер: FPS на слабом устройстве, вес APK, минимальное устройство.
 G3 Раздача: закрытый тест RuStore (проверка) + небольшая VK Реклама на 200–300 «холодных» установок для честного замера D1/D7; сборку подписываем сами.
@@ -415,8 +403,9 @@
 - Баннер ежедневной награды показывается после первого диалога со старостой, а не поверх интро.
 - Квест «Шкуры для торговца» упразднён: вместо него намёк старосты (торговец платит за шкуры, вторая стая к югу).
 - Новые инструменты для карты: спавнер волка возле игрока и граница мира (туман + невидимая стена); расстановка — Ринат.
-- Окна магазина и инвентаря пересобраны на канвас-раскладку для настройки мышкой (доводка выделения кнопок — в работе).</t>
-    </r>
+- Окна магазина, инвентаря и панель статов пересобраны на канвас-раскладку: каждый элемент тянется мышкой (замки на начинке), стилизация владельца перенесена автоматически.
+- Индикация хромоты: плашка «Ранен: скорость снижена» + разовая подсказка, что скорость вернётся после лечения.
+- Граница мира доведена: Volume-поведение при масштабировании, градиентный туман вместо заглушки, горизонтальные полосы тумана для вида сверху с ручкой «толщины» (FogDepth).</t>
   </si>
 </sst>
 </file>
@@ -993,7 +982,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="150.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="208" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>8</v>
       </c>

--- a/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
+++ b/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\game-dev-team\docs\contrary-survivor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD76C2DA-A487-404B-93CE-90DF5B782843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{860E7E66-6C27-459B-9ED2-58239ECE6DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -405,7 +405,9 @@
 - Новые инструменты для карты: спавнер волка возле игрока и граница мира (туман + невидимая стена); расстановка — Ринат.
 - Окна магазина, инвентаря и панель статов пересобраны на канвас-раскладку: каждый элемент тянется мышкой (замки на начинке), стилизация владельца перенесена автоматически.
 - Индикация хромоты: плашка «Ранен: скорость снижена» + разовая подсказка, что скорость вернётся после лечения.
-- Граница мира доведена: Volume-поведение при масштабировании, градиентный туман вместо заглушки, горизонтальные полосы тумана для вида сверху с ручкой «толщины» (FogDepth).</t>
+- Граница мира доведена: Volume-поведение при масштабировании, градиентный туман вместо заглушки, горизонтальные полосы тумана для вида сверху с ручкой «толщины» (FogDepth).
+- Окна диалога и экрана смерти переведены на канвас-раскладку: кнопки тянутся и двигаются мышкой, как в магазине; расстановка, сделанная мышкой, теперь автоматически переносится при пересборках окон (починен перенос геометрии слотов).
+- Туман границы мира переделан: узор из мировых координат без растяжки и швов, два слоя с медленным клублением, рваный мягкий край, углы без двойной яркости; у невидимой стены — отдельная ручка отступа от края карты.</t>
   </si>
 </sst>
 </file>
@@ -982,7 +984,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="208" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="260" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>8</v>
       </c>

--- a/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
+++ b/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\game-dev-team\docs\contrary-survivor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{860E7E66-6C27-459B-9ED2-58239ECE6DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EFE4332-9C30-4E39-963B-089A5DFC7130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -118,34 +118,6 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Этап I — Перевод существующего интерфейса на UMG</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-HUD, магазин, диалоги, экран смерти, инвентарь с иконками → UMG (логика в C++-базе, внешний вид в BP-виджетах WBP_*).
-Новые экраны (онбординг, ежедневка, цифры урона) сразу делаются лёгкими UMG-виджетами.
-Миникарта — в будущем, после тест-билда (до неё игрока ведут метки целей).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>Этап K — Финал / стабилизация / гейт качества</t>
     </r>
     <r>
@@ -408,6 +380,33 @@
 - Граница мира доведена: Volume-поведение при масштабировании, градиентный туман вместо заглушки, горизонтальные полосы тумана для вида сверху с ручкой «толщины» (FogDepth).
 - Окна диалога и экрана смерти переведены на канвас-раскладку: кнопки тянутся и двигаются мышкой, как в магазине; расстановка, сделанная мышкой, теперь автоматически переносится при пересборках окон (починен перенос геометрии слотов).
 - Туман границы мира переделан: узор из мировых координат без растяжки и швов, два слоя с медленным клублением, рваный мягкий край, углы без двойной яркости; у невидимой стены — отдельная ручка отступа от края карты.</t>
+  </si>
+  <si>
+    <r>
+      <t>Этап I — Перевод существующего интерфейса на UMG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+HUD, магазин, диалоги, экран смерти, инвентарь с иконками → UMG (логика в C++-базе, внешний вид в BP-виджетах WBP_*).
+Новые экраны (онбординг, ежедневка, цифры урона) сразу делаются лёгкими UMG-виджетами.
+Миникарта — в будущем, после тест-билда (до неё игрока ведут метки целей).
+Итог этапа: весь интерфейс на UMG — проверено составом ассетов и C++-классов (Ринат закрыл этап 07-28).
+Дополнительно (сверх плана этапа):
++ окна собираются не руками в редакторе, а кодом (инструмент GenerateWbp с режимами пересборки, проверки и снятия среза раскладки) — сборка воспроизводима и проверяема;
++ канвас-раскладка: любой элемент окна двигается и растягивается мышкой, начинка кнопок под замками, чтобы клик выделял саму кнопку;
++ ручная стилизация и расстановка владельца автоматически переносятся при пересборке окон;
++ добавлены экраны и виджеты сверх списка: вступление, пауза, тач-управление для телефона, подсказка хромоты, трекер целей квеста;
++ тексты интерфейса переведены на штатную систему локализации движка (ADR-050);
++ отклонение по букве плана: всплывающие цифры урона сделаны прямой отрисовкой в HUD, а не отдельным UMG-виджетом — так легче для слабых телефонов.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -894,7 +893,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>6</v>
@@ -908,7 +907,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>7</v>
@@ -922,7 +921,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>8</v>
@@ -936,7 +935,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>9</v>
@@ -950,7 +949,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>10</v>
@@ -964,7 +963,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>11</v>
@@ -978,7 +977,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>12</v>
@@ -989,13 +988,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>31</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="50.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1010,18 +1009,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="100" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="175.5" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>10</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>19</v>
+        <v>5</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>34</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="75.5" x14ac:dyDescent="0.25">
@@ -1030,7 +1029,7 @@
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>14</v>
@@ -1042,7 +1041,7 @@
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>15</v>
@@ -1054,7 +1053,7 @@
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>16</v>
@@ -1066,7 +1065,7 @@
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>17</v>

--- a/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
+++ b/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\game-dev-team\docs\contrary-survivor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EFE4332-9C30-4E39-963B-089A5DFC7130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD55843-18BA-4AB3-BAB7-B049199711FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -365,6 +365,33 @@
 07-19: все 7 панелей переведены в UMG (генерация коммандлетом + назначение в слоты, verify вторым процессом, тесты 16/16). Получено ревью publisher: графика проходит, главная дыра - английские надписи и служебные имена в интерфейсе (ADR-049).</t>
   </si>
   <si>
+    <r>
+      <t>Этап I — Перевод существующего интерфейса на UMG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+HUD, магазин, диалоги, экран смерти, инвентарь с иконками → UMG (логика в C++-базе, внешний вид в BP-виджетах WBP_*).
+Новые экраны (онбординг, ежедневка, цифры урона) сразу делаются лёгкими UMG-виджетами.
+Миникарта — в будущем, после тест-билда (до неё игрока ведут метки целей).
+Итог этапа: весь интерфейс на UMG — проверено составом ассетов и C++-классов (Ринат закрыл этап 07-28).
+Дополнительно (сверх плана этапа):
++ окна собираются не руками в редакторе, а кодом (инструмент GenerateWbp с режимами пересборки, проверки и снятия среза раскладки) — сборка воспроизводима и проверяема;
++ канвас-раскладка: любой элемент окна двигается и растягивается мышкой, начинка кнопок под замками, чтобы клик выделял саму кнопку;
++ ручная стилизация и расстановка владельца автоматически переносятся при пересборке окон;
++ добавлены экраны и виджеты сверх списка: вступление, пауза, тач-управление для телефона, подсказка хромоты, трекер целей квеста;
++ тексты интерфейса переведены на штатную систему локализации движка (ADR-050);
++ отклонение по букве плана: всплывающие цифры урона сделаны прямой отрисовкой в HUD, а не отдельным UMG-виджетом — так легче для слабых телефонов.</t>
+    </r>
+  </si>
+  <si>
     <t>Этап G — Android-сборка + замер → BUILD 1
 G1 Первая Android-сборка (без Lumen/Nanite, запечённый свет, цвет в вершинах).
 G2 Замер: FPS на слабом устройстве, вес APK, минимальное устройство.
@@ -379,34 +406,12 @@
 - Индикация хромоты: плашка «Ранен: скорость снижена» + разовая подсказка, что скорость вернётся после лечения.
 - Граница мира доведена: Volume-поведение при масштабировании, градиентный туман вместо заглушки, горизонтальные полосы тумана для вида сверху с ручкой «толщины» (FogDepth).
 - Окна диалога и экрана смерти переведены на канвас-раскладку: кнопки тянутся и двигаются мышкой, как в магазине; расстановка, сделанная мышкой, теперь автоматически переносится при пересборках окон (починен перенос геометрии слотов).
-- Туман границы мира переделан: узор из мировых координат без растяжки и швов, два слоя с медленным клублением, рваный мягкий край, углы без двойной яркости; у невидимой стены — отдельная ручка отступа от края карты.</t>
-  </si>
-  <si>
-    <r>
-      <t>Этап I — Перевод существующего интерфейса на UMG</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-HUD, магазин, диалоги, экран смерти, инвентарь с иконками → UMG (логика в C++-базе, внешний вид в BP-виджетах WBP_*).
-Новые экраны (онбординг, ежедневка, цифры урона) сразу делаются лёгкими UMG-виджетами.
-Миникарта — в будущем, после тест-билда (до неё игрока ведут метки целей).
-Итог этапа: весь интерфейс на UMG — проверено составом ассетов и C++-классов (Ринат закрыл этап 07-28).
-Дополнительно (сверх плана этапа):
-+ окна собираются не руками в редакторе, а кодом (инструмент GenerateWbp с режимами пересборки, проверки и снятия среза раскладки) — сборка воспроизводима и проверяема;
-+ канвас-раскладка: любой элемент окна двигается и растягивается мышкой, начинка кнопок под замками, чтобы клик выделял саму кнопку;
-+ ручная стилизация и расстановка владельца автоматически переносятся при пересборке окон;
-+ добавлены экраны и виджеты сверх списка: вступление, пауза, тач-управление для телефона, подсказка хромоты, трекер целей квеста;
-+ тексты интерфейса переведены на штатную систему локализации движка (ADR-050);
-+ отклонение по букве плана: всплывающие цифры урона сделаны прямой отрисовкой в HUD, а не отдельным UMG-виджетом — так легче для слабых телефонов.</t>
-    </r>
+- Туман границы мира переделан: узор из мировых координат без растяжки и швов, два слоя с медленным клублением, рваный мягкий край, углы без двойной яркости; у невидимой стены — отдельная ручка отступа от края карты.
+- Кнопка бега светится синим и пульсирует, пока включён режим бега.
+- Перед игроком подсвечивается сектор в 100 градусов, и урон холодным оружием наносится ровно в нём: подсветка берёт угол и дальность из самого оружия, поэтому что видно, то и бьёт.
+- Игрок и бандиты при стрельбе доворачивают корпус к противнику: поза прицеливания накладывается только на верх тела, ноги продолжают обычную ходьбу.
+- Удар ножом получил размашистую анимацию замаха, и урон приходит в момент прохода клинка, а не по нажатию кнопки. Анимация не привязана к ножу и подойдёт другому холодному оружию.
+- Собрано и проверено сборкой, автотестами и проверкой схемы анимации; ждёт живой приёмки в игре.</t>
   </si>
 </sst>
 </file>
@@ -983,7 +988,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="260" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="364" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>8</v>
       </c>
@@ -991,7 +996,7 @@
         <v>30</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>31</v>
@@ -1017,7 +1022,7 @@
         <v>5</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>32</v>

--- a/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
+++ b/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\game-dev-team\docs\contrary-survivor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD55843-18BA-4AB3-BAB7-B049199711FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68956A50-DC7B-4A62-8B70-296DC7A512E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -411,7 +411,15 @@
 - Перед игроком подсвечивается сектор в 100 градусов, и урон холодным оружием наносится ровно в нём: подсветка берёт угол и дальность из самого оружия, поэтому что видно, то и бьёт.
 - Игрок и бандиты при стрельбе доворачивают корпус к противнику: поза прицеливания накладывается только на верх тела, ноги продолжают обычную ходьбу.
 - Удар ножом получил размашистую анимацию замаха, и урон приходит в момент прохода клинка, а не по нажатию кнопки. Анимация не привязана к ножу и подойдёт другому холодному оружию.
-- Собрано и проверено сборкой, автотестами и проверкой схемы анимации; ждёт живой приёмки в игре.</t>
+- Собрано и проверено сборкой, автотестами и проверкой схемы анимации; ждёт живой приёмки в игре.
+- Сценка старосты после сдачи ноутбука переписана: он рассказывает про охоту на волков, шкуры и новый завоз у торговца (новая броня, скоро оружие), это заработок, а не квест.
+- Через полминуты после этой сценки один раз за сохранение показывается компактное сообщение о конце сюжета текущей версии с кнопками «Написать мне» (ссылка появится позже) и «Играть дальше».
+- Маркеры показываются по необходимости: после интро виден только маркер деревни, у деревни он сменяется маркером старосты, дальше остаются только квестовые.
+- Три точки рекламы за награду по ТЗ издателя работают на временной заглушке ролика: спасение рюкзака на экране смерти, продажа на половину дороже у торговца и удвоение ежедневной награды; события аналитики уходят по-настоящему.
+- Потери при смерти стали ощутимее: теряется 70 процентов расходников и половина денег, а после просмотра ролика — только по 10 процентов; половина потерянного падает мешком на месте гибели.
+- Появились анимации смерти: бандиты ложатся на спину, волки на бок; волк перекрашен из коричневого в серый; серый шар лута заменён вещмешком, а у волков — свёртком шкуры.
+- Положение пистолета в руке теперь настраивается наглядно перемещением сокета в редакторе скелета; торговец получил собственную модель по референсу.
+- Всё собрано и проверено чистой пересборкой, 26 автотестами и проверками ассетов; волна ждёт живой приёмки в игре.</t>
   </si>
 </sst>
 </file>
@@ -988,7 +996,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="364" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>8</v>
       </c>

--- a/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
+++ b/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\game-dev-team\docs\contrary-survivor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68956A50-DC7B-4A62-8B70-296DC7A512E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE989D82-542D-4726-B676-31B81D056B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -419,7 +419,15 @@
 - Потери при смерти стали ощутимее: теряется 70 процентов расходников и половина денег, а после просмотра ролика — только по 10 процентов; половина потерянного падает мешком на месте гибели.
 - Появились анимации смерти: бандиты ложатся на спину, волки на бок; волк перекрашен из коричневого в серый; серый шар лута заменён вещмешком, а у волков — свёртком шкуры.
 - Положение пистолета в руке теперь настраивается наглядно перемещением сокета в редакторе скелета; торговец получил собственную модель по референсу.
-- Всё собрано и проверено чистой пересборкой, 26 автотестами и проверками ассетов; волна ждёт живой приёмки в игре.</t>
+- Всё собрано и проверено чистой пересборкой, 26 автотестами и проверками ассетов; волна ждёт живой приёмки в игре.
+Волна Build 1.2.1 (ночь 02.08, по замечаниям живой приёмки Build 1.2):
+- Трупы волков и бандитов теперь можно обыскивать: подсказка у трупа, окно выбора добычи с забором по клику и кнопкой «Забрать всё», недобранное остаётся в трупе, труп лежит настраиваемые 60 секунд.
+- Починены «серые» мешки и свёртки: в моделях сидел служебный шахматный материал движка, заменён на игровой; свёрток шкуры больше не микроскопический; у вещмешка появилось настраиваемое свечение с пульсацией (по умолчанию выключено).
+- Порог доступности рекламы снижен с 15 до 6 минут и настраивается без пересборки; добавлена отладочная клавиша F, мгновенно открывающая рекламные кнопки для проверки.
+- Шкуры, тушёнка и аптечки складываются в стопки как патроны: подбор, продажа ползунком, потери при смерти и зачёт квеста работают по штукам (покрыто автотестами).
+- При гибели герой ложится на спину той же анимацией, что и бандиты, и штатно оживает при возрождении.
+- Все 12 окон интерфейса разлочены по задаче Рината: каждый текст и каждая кнопка лежат на свободном поле и двигаются мышкой в редакторе; прежняя ручная расстановка перенесена один в один; памятка по окнам обновлена.
+- Волна проверена полной чистой пересборкой, 32 автотестами и проверками всех окон; ждёт живой приёмки в игре, после неё обе волны вливаются в основную ветку.</t>
   </si>
 </sst>
 </file>

--- a/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
+++ b/docs/contrary-survivor/DemoPlanTemplateRec.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\game-dev-team\docs\contrary-survivor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE989D82-542D-4726-B676-31B81D056B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{066DECBD-4DAC-4FFE-89AB-F14BD3F0EBD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -427,7 +427,20 @@
 - Шкуры, тушёнка и аптечки складываются в стопки как патроны: подбор, продажа ползунком, потери при смерти и зачёт квеста работают по штукам (покрыто автотестами).
 - При гибели герой ложится на спину той же анимацией, что и бандиты, и штатно оживает при возрождении.
 - Все 12 окон интерфейса разлочены по задаче Рината: каждый текст и каждая кнопка лежат на свободном поле и двигаются мышкой в редакторе; прежняя ручная расстановка перенесена один в один; памятка по окнам обновлена.
-- Волна проверена полной чистой пересборкой, 32 автотестами и проверками всех окон; ждёт живой приёмки в игре, после неё обе волны вливаются в основную ветку.</t>
+- Волна проверена полной чистой пересборкой, 32 автотестами и проверками всех окон; ждёт живой приёмки в игре, после неё обе волны вливаются в основную ветку.
+Подготовка к первой выкладке на RuStore (05–06.08): ревизия издателя и задание Б1–Б10:
+- Проведена полная ревизия игры на живом телефоне (запуск, прохождение, кадры, журнал), отчёт принят издателем; по итогам издатель выдал задание из десяти пунктов Б1–Б10, работы шли строго по порядку.
+- Б1: ассеты, терявшиеся при упаковке (анимация смерти людей, сектор удара ножа), возвращены в сборку — бандиты и игрок снова падают при смерти, сектор ножа виден.
+- Б2: починена продажа стопками (раньше всё, кроме патронов, продавалось только по одной штуке), после этого заработала и золотая кнопка «продать дороже за просмотр ролика».
+- Б3: сохранение теперь читается при запуске игры — игра различает «новую игру» и «продолжить», вступительная сценка показывается только новым игрокам.
+- Б4: аналитика получила настоящие ключи, вшиваемые при сборке, и события первого запуска, шагов и завершения обучения; живая доставка событий на сервер пока не проверялась.
+- Б5: публикационная сборка Shipping — все отладочные клавиши и счётчики вырезаны из кода при компиляции, подписи компьютерных клавиш убраны с экрана телефона.
+- Б6: при первом запуске показывается экран согласия на обработку данных со ссылкой на политику конфиденциальности (тексты написаны, страница политики готова и ждёт публикации по постоянному адресу).
+- Б7: экономика — новый игрок начинает только с ножом, пистолет стал первой целью накопления (150 монет у торговца), шкура волка подорожала с 2 до 15 монет, закрыта дыра «вода покупается за 5 и продаётся за 6».
+- Б8: вёрстка магазина под телефон — сетка товаров растянута на пустовавшую половину экрана, колонки считаются по реальной ширине, подписи брони влезают в плитки.
+- Б9: сборка объявляет поддержку вытянутых экранов (2.22 вместо 2.1) — чёрные поля по краям ушли; полосы здоровья и голода отодвинуты от выреза камеры.
+- Создан ключ подписи для RuStore (хранить вечно: без него нельзя выпустить ни одно обновление); собран дистрибуционный пак Shipping с релизной подписью и выключенным флагом отладки.
+- Осталось до выкладки: Б10 боевая реклама (три отдельных рекламных блока, ждёт рекламный кабинет Рината), публикация страницы политики в интернете, карточка игры в магазине RuStore.</t>
   </si>
 </sst>
 </file>
